--- a/.buildkite/test_selection_skills/vLLm forced-merge PRs.xlsx
+++ b/.buildkite/test_selection_skills/vLLm forced-merge PRs.xlsx
@@ -1,302 +1,296 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="07May-06June" sheetId="1" r:id="rId5"/>
+    <sheet name="07May-06June" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="70">
-  <si>
-    <t>PR URL</t>
-  </si>
-  <si>
-    <t>Author</t>
-  </si>
-  <si>
-    <t>Slack Date</t>
-  </si>
-  <si>
-    <t>Slack User</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/43167</t>
-  </si>
-  <si>
-    <t>CI Fails on Main as well</t>
-  </si>
-  <si>
-    <t>Harry Mellor</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/44484</t>
-  </si>
-  <si>
-    <t>Unrelated CI failures</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/43720</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/43543</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/40470</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/42083</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/37505</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/44036</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/43383</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/43581</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/43583</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/43824</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/43045</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/42129</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/43358</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/44244</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/42343</t>
-  </si>
-  <si>
-    <t>Wei Zhao</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/41471</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/43325</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/43556</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/43838</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/43339</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/43571</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>https://github.com/vllm-project/vllm/pull/42554</t>
-    </r>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/43871</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/43972</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/42288</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/40172</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/42224</t>
-  </si>
-  <si>
-    <t>Yange Liu</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/41261</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/42913</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/41972</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/42070</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/42975</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>https://github.com/vllm-project/vllm/pull/37888</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>https://github.com/vllm-project/vllm/pull/42950</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>https://github.com/vllm-project/vllm/pull/42951</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>https://github.com/vllm-project/vllm/pull/42952</t>
-    </r>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/42767</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/41802</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/42630</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/39337</t>
-  </si>
-  <si>
-    <t>Doc build issue</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/42676</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/40717</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/42849</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/43140</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>https://github.com/vllm-project/vllm/pull/38973</t>
-    </r>
-    <r>
-      <rPr/>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <t>doc build stuck</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/39601</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/43286</t>
-  </si>
-  <si>
-    <t>Unrelated and Flaky</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/40392</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/40269</t>
-  </si>
-  <si>
-    <t>Flaky</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/41991</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/43260</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/41979</t>
-  </si>
-  <si>
-    <t>CI fails on Main as well</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/41252</t>
-  </si>
-  <si>
-    <t>https://github.com/vllm-project/vllm/pull/43230</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="71">
+  <si>
+    <t xml:space="preserve">PR URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Author</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slack Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slack User</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/43167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI Fails on Main as well</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harry Mellor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/44484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unrelated CI failures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/43720</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/43543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/40470</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/42083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/37505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/44036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/43383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/43581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/43583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/43824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/43045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/42129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/43358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/44244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/42343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wei Zhao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/41471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/43325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/43556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/43838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/43339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/43571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/42554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/43871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/43972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/42288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/40172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/42224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yange Liu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/41261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/42913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/41972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/42070</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/42975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/37888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/42950</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/42951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/42952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/42767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/41802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/42630</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/39337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doc build issue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/42676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/40717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/42849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/43140</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/38973 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">doc build stuck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/39601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/43286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unrelated and Flaky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/40392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/40269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flaky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/41991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/43260</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/41979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI fails on Main as well</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/41252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/43230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/vllm-project/vllm/pull/44999</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="d mmmm"/>
-    <numFmt numFmtId="165" formatCode="d mmm"/>
-    <numFmt numFmtId="166" formatCode="dmmmm"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="5">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="d\ mmmm"/>
+    <numFmt numFmtId="166" formatCode="d\ mmm"/>
+    <numFmt numFmtId="167" formatCode="dmmmm"/>
+    <numFmt numFmtId="168" formatCode="mm/dd/yy"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="7">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
-      <u/>
+      <u val="single"/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <color rgb="FF0000FF"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -304,76 +298,167 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFCCCCCC"/>
-        <bgColor rgb="FFCCCCCC"/>
+        <bgColor rgb="FFCCCCFF"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="2">
-    <border/>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="10">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFCCCCCC"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -384,94 +469,90 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4285F4"/>
+        <a:srgbClr val="4285f4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EA4335"/>
+        <a:srgbClr val="ea4335"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="FBBC04"/>
+        <a:srgbClr val="fbbc04"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="34A853"/>
+        <a:srgbClr val="34a853"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="FF6D01"/>
+        <a:srgbClr val="ff6d01"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="46BDC6"/>
+        <a:srgbClr val="46bdc6"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="1155cc"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="1155cc"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -479,33 +560,24 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
@@ -518,13 +590,7 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -534,15 +600,13 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
-            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -550,7 +614,6 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -558,11 +621,11 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
-                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -571,17 +634,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <outlinePr summaryBelow="0"/>
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:E63"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="42.38"/>
-    <col customWidth="1" min="4" max="4" width="18.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18.63"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -596,13 +661,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="4"/>
-      <c r="C2" s="5">
-        <v>46178.0</v>
+      <c r="C2" s="5" t="n">
+        <v>46178</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>5</v>
@@ -611,193 +676,193 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="7" t="s">
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="4"/>
-      <c r="C3" s="5">
-        <v>46178.0</v>
+      <c r="C3" s="5" t="n">
+        <v>46178</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="4"/>
     </row>
-    <row r="4">
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="4"/>
-      <c r="C4" s="5">
-        <v>46178.0</v>
+      <c r="C4" s="5" t="n">
+        <v>46178</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="4"/>
     </row>
-    <row r="5">
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="4"/>
-      <c r="C5" s="5">
-        <v>46168.0</v>
+      <c r="C5" s="5" t="n">
+        <v>46168</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
     </row>
-    <row r="6">
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="4"/>
-      <c r="C6" s="5">
-        <v>46176.0</v>
+      <c r="C6" s="5" t="n">
+        <v>46176</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
     </row>
-    <row r="7">
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="4"/>
-      <c r="C7" s="5">
-        <v>46170.0</v>
+      <c r="C7" s="5" t="n">
+        <v>46170</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
     </row>
-    <row r="8">
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B8" s="4"/>
-      <c r="C8" s="5">
-        <v>46176.0</v>
+      <c r="C8" s="5" t="n">
+        <v>46176</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
     </row>
-    <row r="9">
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="4"/>
-      <c r="C9" s="5">
-        <v>46175.0</v>
+      <c r="C9" s="5" t="n">
+        <v>46175</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
     </row>
-    <row r="10">
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B10" s="4"/>
-      <c r="C10" s="5">
-        <v>46165.0</v>
+      <c r="C10" s="5" t="n">
+        <v>46165</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
     </row>
-    <row r="11">
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B11" s="4"/>
-      <c r="C11" s="5">
-        <v>46170.0</v>
+      <c r="C11" s="5" t="n">
+        <v>46170</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
     </row>
-    <row r="12">
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B12" s="4"/>
-      <c r="C12" s="5">
-        <v>46167.0</v>
+      <c r="C12" s="5" t="n">
+        <v>46167</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
     </row>
-    <row r="13">
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
         <v>18</v>
       </c>
       <c r="B13" s="4"/>
-      <c r="C13" s="5">
-        <v>46170.0</v>
+      <c r="C13" s="5" t="n">
+        <v>46170</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
     </row>
-    <row r="14">
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B14" s="4"/>
-      <c r="C14" s="5">
-        <v>46168.0</v>
+      <c r="C14" s="5" t="n">
+        <v>46168</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
     </row>
-    <row r="15">
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="4"/>
-      <c r="C15" s="5">
-        <v>46177.0</v>
+      <c r="C15" s="5" t="n">
+        <v>46177</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
     </row>
-    <row r="16">
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
         <v>21</v>
       </c>
       <c r="B16" s="4"/>
-      <c r="C16" s="5">
-        <v>46169.0</v>
+      <c r="C16" s="5" t="n">
+        <v>46169</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
     </row>
-    <row r="17">
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B17" s="4"/>
-      <c r="C17" s="5">
-        <v>46170.0</v>
+      <c r="C17" s="5" t="n">
+        <v>46170</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
     </row>
-    <row r="18">
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B18" s="4"/>
-      <c r="C18" s="5">
-        <v>46175.0</v>
+      <c r="C18" s="5" t="n">
+        <v>46175</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
     </row>
-    <row r="19">
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="4"/>
-      <c r="C19" s="5">
-        <v>46170.0</v>
+      <c r="C19" s="5" t="n">
+        <v>46170</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>8</v>
@@ -806,68 +871,68 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B20" s="4"/>
-      <c r="C20" s="5">
-        <v>46169.0</v>
+      <c r="C20" s="5" t="n">
+        <v>46169</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
     </row>
-    <row r="21">
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
         <v>26</v>
       </c>
       <c r="B21" s="4"/>
-      <c r="C21" s="5">
-        <v>46168.0</v>
+      <c r="C21" s="5" t="n">
+        <v>46168</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
     </row>
-    <row r="22">
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
         <v>27</v>
       </c>
       <c r="B22" s="4"/>
-      <c r="C22" s="8">
-        <v>46176.0</v>
+      <c r="C22" s="7" t="n">
+        <v>46176</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
     </row>
-    <row r="23">
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
         <v>28</v>
       </c>
       <c r="B23" s="4"/>
-      <c r="C23" s="8">
-        <v>46176.0</v>
+      <c r="C23" s="7" t="n">
+        <v>46176</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
     </row>
-    <row r="24">
-      <c r="A24" s="7" t="s">
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B24" s="4"/>
-      <c r="C24" s="8">
-        <v>46176.0</v>
+      <c r="C24" s="7" t="n">
+        <v>46176</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
     </row>
-    <row r="25">
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B25" s="4"/>
-      <c r="C25" s="8">
-        <v>46175.0</v>
+      <c r="C25" s="7" t="n">
+        <v>46175</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>8</v>
@@ -876,523 +941,537 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B26" s="4"/>
-      <c r="C26" s="5">
-        <v>46172.0</v>
+      <c r="C26" s="5" t="n">
+        <v>46172</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
     </row>
-    <row r="27">
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B27" s="4"/>
-      <c r="C27" s="8">
-        <v>46177.0</v>
+      <c r="C27" s="7" t="n">
+        <v>46177</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
     </row>
-    <row r="28">
+    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B28" s="4"/>
-      <c r="C28" s="5">
-        <v>46171.0</v>
+      <c r="C28" s="5" t="n">
+        <v>46171</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
     </row>
-    <row r="29">
+    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B29" s="4"/>
-      <c r="C29" s="5">
-        <v>46171.0</v>
+      <c r="C29" s="5" t="n">
+        <v>46171</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
     </row>
-    <row r="30">
+    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
         <v>34</v>
       </c>
       <c r="B30" s="4"/>
-      <c r="C30" s="5">
-        <v>46170.0</v>
+      <c r="C30" s="5" t="n">
+        <v>46170</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
     </row>
-    <row r="31">
+    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B31" s="4"/>
-      <c r="C31" s="5">
-        <v>46170.0</v>
+      <c r="C31" s="5" t="n">
+        <v>46170</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
     </row>
-    <row r="32">
+    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B32" s="4"/>
-      <c r="C32" s="8">
-        <v>46176.0</v>
+      <c r="C32" s="7" t="n">
+        <v>46176</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
     </row>
-    <row r="33">
+    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B33" s="4"/>
-      <c r="C33" s="9">
-        <v>46163.0</v>
+      <c r="C33" s="8" t="n">
+        <v>46163</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
     </row>
-    <row r="34">
+    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B34" s="4"/>
-      <c r="C34" s="5">
-        <v>46159.0</v>
+      <c r="C34" s="5" t="n">
+        <v>46159</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B35" s="4"/>
-      <c r="C35" s="5">
-        <v>46155.0</v>
+      <c r="C35" s="5" t="n">
+        <v>46155</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
     </row>
-    <row r="36">
+    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
         <v>39</v>
       </c>
       <c r="B36" s="4"/>
-      <c r="C36" s="5">
-        <v>46160.0</v>
+      <c r="C36" s="5" t="n">
+        <v>46160</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
     </row>
-    <row r="37">
+    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B37" s="4"/>
-      <c r="C37" s="5">
-        <v>46160.0</v>
+      <c r="C37" s="5" t="n">
+        <v>46160</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>8</v>
       </c>
       <c r="E37" s="4"/>
     </row>
-    <row r="38">
+    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
       <c r="B38" s="4"/>
-      <c r="C38" s="5">
-        <v>46150.0</v>
+      <c r="C38" s="5" t="n">
+        <v>46150</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
     </row>
-    <row r="39">
+    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B39" s="4"/>
-      <c r="C39" s="5">
-        <v>46151.0</v>
+      <c r="C39" s="5" t="n">
+        <v>46151</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
     </row>
-    <row r="40">
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
         <v>42</v>
       </c>
       <c r="B40" s="4"/>
-      <c r="C40" s="5">
-        <v>46161.0</v>
+      <c r="C40" s="5" t="n">
+        <v>46161</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>8</v>
       </c>
       <c r="E40" s="4"/>
     </row>
-    <row r="41">
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
         <v>43</v>
       </c>
       <c r="B41" s="4"/>
-      <c r="C41" s="5">
-        <v>46163.0</v>
+      <c r="C41" s="5" t="n">
+        <v>46163</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>5</v>
       </c>
       <c r="E41" s="4"/>
     </row>
-    <row r="42">
+    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
         <v>44</v>
       </c>
       <c r="B42" s="4"/>
-      <c r="C42" s="5">
-        <v>46163.0</v>
+      <c r="C42" s="5" t="n">
+        <v>46163</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>5</v>
       </c>
       <c r="E42" s="4"/>
     </row>
-    <row r="43">
+    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
         <v>45</v>
       </c>
       <c r="B43" s="4"/>
-      <c r="C43" s="5">
-        <v>46163.0</v>
+      <c r="C43" s="5" t="n">
+        <v>46163</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>5</v>
       </c>
       <c r="E43" s="4"/>
     </row>
-    <row r="44">
+    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
       <c r="B44" s="4"/>
-      <c r="C44" s="5">
-        <v>46163.0</v>
+      <c r="C44" s="5" t="n">
+        <v>46163</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>5</v>
       </c>
       <c r="E44" s="4"/>
     </row>
-    <row r="45">
+    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
         <v>47</v>
       </c>
       <c r="B45" s="4"/>
-      <c r="C45" s="5">
-        <v>46160.0</v>
+      <c r="C45" s="5" t="n">
+        <v>46160</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>8</v>
       </c>
       <c r="E45" s="4"/>
     </row>
-    <row r="46">
+    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
       <c r="B46" s="4"/>
-      <c r="C46" s="5">
-        <v>46151.0</v>
+      <c r="C46" s="5" t="n">
+        <v>46151</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>8</v>
       </c>
       <c r="E46" s="4"/>
     </row>
-    <row r="47">
+    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
         <v>49</v>
       </c>
       <c r="B47" s="4"/>
-      <c r="C47" s="5">
-        <v>46157.0</v>
+      <c r="C47" s="5" t="n">
+        <v>46157</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>5</v>
       </c>
       <c r="E47" s="4"/>
     </row>
-    <row r="48">
+    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
       <c r="B48" s="4"/>
-      <c r="C48" s="5">
-        <v>46156.0</v>
+      <c r="C48" s="5" t="n">
+        <v>46156</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>51</v>
       </c>
       <c r="E48" s="4"/>
     </row>
-    <row r="49">
+    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
         <v>52</v>
       </c>
       <c r="B49" s="4"/>
-      <c r="C49" s="5">
-        <v>46157.0</v>
+      <c r="C49" s="5" t="n">
+        <v>46157</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>51</v>
       </c>
       <c r="E49" s="4"/>
     </row>
-    <row r="50">
+    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="s">
         <v>53</v>
       </c>
       <c r="B50" s="4"/>
-      <c r="C50" s="5">
-        <v>46161.0</v>
+      <c r="C50" s="5" t="n">
+        <v>46161</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
     </row>
-    <row r="51">
+    <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
         <v>54</v>
       </c>
       <c r="B51" s="4"/>
-      <c r="C51" s="5">
-        <v>46160.0</v>
+      <c r="C51" s="5" t="n">
+        <v>46160</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>8</v>
       </c>
       <c r="E51" s="4"/>
     </row>
-    <row r="52">
+    <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
         <v>55</v>
       </c>
       <c r="B52" s="4"/>
-      <c r="C52" s="5">
-        <v>46163.0</v>
+      <c r="C52" s="5" t="n">
+        <v>46163</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
     </row>
-    <row r="53">
-      <c r="A53" s="7" t="s">
+    <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="3" t="s">
         <v>56</v>
       </c>
       <c r="B53" s="4"/>
-      <c r="C53" s="5">
-        <v>46163.0</v>
+      <c r="C53" s="5" t="n">
+        <v>46163</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>57</v>
       </c>
       <c r="E53" s="4"/>
     </row>
-    <row r="54">
-      <c r="A54" s="7" t="s">
+    <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="3" t="s">
         <v>58</v>
       </c>
       <c r="B54" s="4"/>
-      <c r="C54" s="5">
-        <v>46163.0</v>
+      <c r="C54" s="5" t="n">
+        <v>46163</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>57</v>
       </c>
       <c r="E54" s="4"/>
     </row>
-    <row r="55">
+    <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
         <v>59</v>
       </c>
       <c r="B55" s="4"/>
-      <c r="C55" s="5">
-        <v>46164.0</v>
+      <c r="C55" s="5" t="n">
+        <v>46164</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>60</v>
       </c>
       <c r="E55" s="4"/>
     </row>
-    <row r="56">
+    <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
         <v>61</v>
       </c>
       <c r="B56" s="4"/>
-      <c r="C56" s="5">
-        <v>46150.0</v>
+      <c r="C56" s="5" t="n">
+        <v>46150</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>8</v>
       </c>
       <c r="E56" s="4"/>
     </row>
-    <row r="57">
+    <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
         <v>62</v>
       </c>
       <c r="B57" s="4"/>
-      <c r="C57" s="5">
-        <v>46156.0</v>
+      <c r="C57" s="5" t="n">
+        <v>46156</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>63</v>
       </c>
       <c r="E57" s="4"/>
     </row>
-    <row r="58">
+    <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
         <v>64</v>
       </c>
       <c r="B58" s="4"/>
-      <c r="C58" s="5">
-        <v>46151.0</v>
+      <c r="C58" s="5" t="n">
+        <v>46151</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>8</v>
       </c>
       <c r="E58" s="4"/>
     </row>
-    <row r="59">
+    <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="3" t="s">
         <v>65</v>
       </c>
       <c r="B59" s="4"/>
-      <c r="C59" s="5">
-        <v>46164.0</v>
+      <c r="C59" s="5" t="n">
+        <v>46164</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>8</v>
       </c>
       <c r="E59" s="4"/>
     </row>
-    <row r="60">
+    <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="3" t="s">
         <v>66</v>
       </c>
       <c r="B60" s="4"/>
-      <c r="C60" s="5">
-        <v>46152.0</v>
+      <c r="C60" s="5" t="n">
+        <v>46152</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>67</v>
       </c>
       <c r="E60" s="4"/>
     </row>
-    <row r="61">
+    <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="3" t="s">
         <v>68</v>
       </c>
       <c r="B61" s="4"/>
-      <c r="C61" s="5">
-        <v>46156.0</v>
+      <c r="C61" s="5" t="n">
+        <v>46156</v>
       </c>
       <c r="D61" s="6" t="s">
         <v>57</v>
       </c>
       <c r="E61" s="4"/>
     </row>
-    <row r="62">
+    <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="3" t="s">
         <v>69</v>
       </c>
       <c r="B62" s="4"/>
-      <c r="C62" s="5">
-        <v>46163.0</v>
+      <c r="C62" s="5" t="n">
+        <v>46163</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>67</v>
       </c>
       <c r="E62" s="4"/>
     </row>
+    <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="C63" s="9" t="n">
+        <v>46182</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="A2"/>
-    <hyperlink r:id="rId2" ref="A3"/>
-    <hyperlink r:id="rId3" ref="A4"/>
-    <hyperlink r:id="rId4" ref="A5"/>
-    <hyperlink r:id="rId5" ref="A6"/>
-    <hyperlink r:id="rId6" ref="A7"/>
-    <hyperlink r:id="rId7" ref="A8"/>
-    <hyperlink r:id="rId8" ref="A9"/>
-    <hyperlink r:id="rId9" ref="A10"/>
-    <hyperlink r:id="rId10" ref="A11"/>
-    <hyperlink r:id="rId11" ref="A12"/>
-    <hyperlink r:id="rId12" ref="A13"/>
-    <hyperlink r:id="rId13" ref="A14"/>
-    <hyperlink r:id="rId14" ref="A15"/>
-    <hyperlink r:id="rId15" ref="A16"/>
-    <hyperlink r:id="rId16" ref="A17"/>
-    <hyperlink r:id="rId17" ref="A18"/>
-    <hyperlink r:id="rId18" ref="A19"/>
-    <hyperlink r:id="rId19" ref="A20"/>
-    <hyperlink r:id="rId20" ref="A21"/>
-    <hyperlink r:id="rId21" ref="A22"/>
-    <hyperlink r:id="rId22" ref="A23"/>
-    <hyperlink r:id="rId23" location="issuecomment-4607421597" ref="A24"/>
-    <hyperlink r:id="rId24" ref="A25"/>
-    <hyperlink r:id="rId25" ref="A26"/>
-    <hyperlink r:id="rId26" ref="A27"/>
-    <hyperlink r:id="rId27" ref="A28"/>
-    <hyperlink r:id="rId28" ref="A29"/>
-    <hyperlink r:id="rId29" ref="A30"/>
-    <hyperlink r:id="rId30" ref="A31"/>
-    <hyperlink r:id="rId31" ref="A32"/>
-    <hyperlink r:id="rId32" ref="A33"/>
-    <hyperlink r:id="rId33" ref="A34"/>
-    <hyperlink r:id="rId34" ref="A35"/>
-    <hyperlink r:id="rId35" ref="A36"/>
-    <hyperlink r:id="rId36" ref="A37"/>
-    <hyperlink r:id="rId37" ref="A38"/>
-    <hyperlink r:id="rId38" ref="A39"/>
-    <hyperlink r:id="rId39" ref="A40"/>
-    <hyperlink r:id="rId40" ref="A41"/>
-    <hyperlink r:id="rId41" ref="A42"/>
-    <hyperlink r:id="rId42" ref="A43"/>
-    <hyperlink r:id="rId43" ref="A44"/>
-    <hyperlink r:id="rId44" ref="A45"/>
-    <hyperlink r:id="rId45" ref="A46"/>
-    <hyperlink r:id="rId46" ref="A47"/>
-    <hyperlink r:id="rId47" ref="A48"/>
-    <hyperlink r:id="rId48" ref="A49"/>
-    <hyperlink r:id="rId49" ref="A50"/>
-    <hyperlink r:id="rId50" ref="A51"/>
-    <hyperlink r:id="rId51" ref="A52"/>
-    <hyperlink r:id="rId52" ref="A53"/>
-    <hyperlink r:id="rId53" ref="A54"/>
-    <hyperlink r:id="rId54" ref="A55"/>
-    <hyperlink r:id="rId55" ref="A56"/>
-    <hyperlink r:id="rId56" ref="A57"/>
-    <hyperlink r:id="rId57" ref="A58"/>
-    <hyperlink r:id="rId58" ref="A59"/>
-    <hyperlink r:id="rId59" ref="A60"/>
-    <hyperlink r:id="rId60" ref="A61"/>
-    <hyperlink r:id="rId61" ref="A62"/>
+    <hyperlink ref="A2" r:id="rId1" display="https://github.com/vllm-project/vllm/pull/43167"/>
+    <hyperlink ref="A3" r:id="rId2" display="https://github.com/vllm-project/vllm/pull/44484"/>
+    <hyperlink ref="A4" r:id="rId3" display="https://github.com/vllm-project/vllm/pull/43720"/>
+    <hyperlink ref="A5" r:id="rId4" display="https://github.com/vllm-project/vllm/pull/43543"/>
+    <hyperlink ref="A6" r:id="rId5" display="https://github.com/vllm-project/vllm/pull/40470"/>
+    <hyperlink ref="A7" r:id="rId6" display="https://github.com/vllm-project/vllm/pull/42083"/>
+    <hyperlink ref="A8" r:id="rId7" display="https://github.com/vllm-project/vllm/pull/37505"/>
+    <hyperlink ref="A9" r:id="rId8" display="https://github.com/vllm-project/vllm/pull/44036"/>
+    <hyperlink ref="A10" r:id="rId9" display="https://github.com/vllm-project/vllm/pull/43383"/>
+    <hyperlink ref="A11" r:id="rId10" display="https://github.com/vllm-project/vllm/pull/43581"/>
+    <hyperlink ref="A12" r:id="rId11" display="https://github.com/vllm-project/vllm/pull/43583"/>
+    <hyperlink ref="A13" r:id="rId12" display="https://github.com/vllm-project/vllm/pull/43824"/>
+    <hyperlink ref="A14" r:id="rId13" display="https://github.com/vllm-project/vllm/pull/43045"/>
+    <hyperlink ref="A15" r:id="rId14" display="https://github.com/vllm-project/vllm/pull/42129"/>
+    <hyperlink ref="A16" r:id="rId15" display="https://github.com/vllm-project/vllm/pull/43358"/>
+    <hyperlink ref="A17" r:id="rId16" display="https://github.com/vllm-project/vllm/pull/43581"/>
+    <hyperlink ref="A18" r:id="rId17" display="https://github.com/vllm-project/vllm/pull/44244"/>
+    <hyperlink ref="A19" r:id="rId18" display="https://github.com/vllm-project/vllm/pull/42343"/>
+    <hyperlink ref="A20" r:id="rId19" display="https://github.com/vllm-project/vllm/pull/41471"/>
+    <hyperlink ref="A21" r:id="rId20" display="https://github.com/vllm-project/vllm/pull/43325"/>
+    <hyperlink ref="A22" r:id="rId21" display="https://github.com/vllm-project/vllm/pull/43556"/>
+    <hyperlink ref="A23" r:id="rId22" display="https://github.com/vllm-project/vllm/pull/43838"/>
+    <hyperlink ref="A24" r:id="rId23" location="issuecomment-4607421597" display="https://github.com/vllm-project/vllm/pull/44036"/>
+    <hyperlink ref="A25" r:id="rId24" display="https://github.com/vllm-project/vllm/pull/43339"/>
+    <hyperlink ref="A26" r:id="rId25" display="https://github.com/vllm-project/vllm/pull/43571"/>
+    <hyperlink ref="A27" r:id="rId26" display="https://github.com/vllm-project/vllm/pull/42554"/>
+    <hyperlink ref="A28" r:id="rId27" display="https://github.com/vllm-project/vllm/pull/43871"/>
+    <hyperlink ref="A29" r:id="rId28" display="https://github.com/vllm-project/vllm/pull/43972"/>
+    <hyperlink ref="A30" r:id="rId29" display="https://github.com/vllm-project/vllm/pull/42288"/>
+    <hyperlink ref="A31" r:id="rId30" display="https://github.com/vllm-project/vllm/pull/42083"/>
+    <hyperlink ref="A32" r:id="rId31" display="https://github.com/vllm-project/vllm/pull/40470"/>
+    <hyperlink ref="A33" r:id="rId32" display="https://github.com/vllm-project/vllm/pull/40172"/>
+    <hyperlink ref="A34" r:id="rId33" display="https://github.com/vllm-project/vllm/pull/42224"/>
+    <hyperlink ref="A35" r:id="rId34" display="https://github.com/vllm-project/vllm/pull/41261"/>
+    <hyperlink ref="A36" r:id="rId35" display="https://github.com/vllm-project/vllm/pull/42913"/>
+    <hyperlink ref="A37" r:id="rId36" display="https://github.com/vllm-project/vllm/pull/40470"/>
+    <hyperlink ref="A38" r:id="rId37" display="https://github.com/vllm-project/vllm/pull/41972"/>
+    <hyperlink ref="A39" r:id="rId38" display="https://github.com/vllm-project/vllm/pull/42070"/>
+    <hyperlink ref="A40" r:id="rId39" display="https://github.com/vllm-project/vllm/pull/42975"/>
+    <hyperlink ref="A41" r:id="rId40" display="https://github.com/vllm-project/vllm/pull/37888"/>
+    <hyperlink ref="A42" r:id="rId41" display="https://github.com/vllm-project/vllm/pull/42950"/>
+    <hyperlink ref="A43" r:id="rId42" display="https://github.com/vllm-project/vllm/pull/42951"/>
+    <hyperlink ref="A44" r:id="rId43" display="https://github.com/vllm-project/vllm/pull/42952"/>
+    <hyperlink ref="A45" r:id="rId44" display="https://github.com/vllm-project/vllm/pull/42767"/>
+    <hyperlink ref="A46" r:id="rId45" display="https://github.com/vllm-project/vllm/pull/41802"/>
+    <hyperlink ref="A47" r:id="rId46" display="https://github.com/vllm-project/vllm/pull/42630"/>
+    <hyperlink ref="A48" r:id="rId47" display="https://github.com/vllm-project/vllm/pull/39337"/>
+    <hyperlink ref="A49" r:id="rId48" display="https://github.com/vllm-project/vllm/pull/42676"/>
+    <hyperlink ref="A50" r:id="rId49" display="https://github.com/vllm-project/vllm/pull/40717"/>
+    <hyperlink ref="A51" r:id="rId50" display="https://github.com/vllm-project/vllm/pull/42849"/>
+    <hyperlink ref="A52" r:id="rId51" display="https://github.com/vllm-project/vllm/pull/43140"/>
+    <hyperlink ref="A53" r:id="rId52" display="https://github.com/vllm-project/vllm/pull/38973 "/>
+    <hyperlink ref="A54" r:id="rId53" display="https://github.com/vllm-project/vllm/pull/39601"/>
+    <hyperlink ref="A55" r:id="rId54" display="https://github.com/vllm-project/vllm/pull/43286"/>
+    <hyperlink ref="A56" r:id="rId55" display="https://github.com/vllm-project/vllm/pull/40392"/>
+    <hyperlink ref="A57" r:id="rId56" display="https://github.com/vllm-project/vllm/pull/40269"/>
+    <hyperlink ref="A58" r:id="rId57" display="https://github.com/vllm-project/vllm/pull/41991"/>
+    <hyperlink ref="A59" r:id="rId58" display="https://github.com/vllm-project/vllm/pull/43260"/>
+    <hyperlink ref="A60" r:id="rId59" display="https://github.com/vllm-project/vllm/pull/41979"/>
+    <hyperlink ref="A61" r:id="rId60" display="https://github.com/vllm-project/vllm/pull/41252"/>
+    <hyperlink ref="A62" r:id="rId61" display="https://github.com/vllm-project/vllm/pull/43230"/>
   </hyperlinks>
-  <drawing r:id="rId62"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>